--- a/artfynd/A 29101-2024 artfynd.xlsx
+++ b/artfynd/A 29101-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118550742</v>
+        <v>118550760</v>
       </c>
       <c r="B2" t="n">
-        <v>90469</v>
+        <v>90504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Mellgårdssjöberget (Mellgårdssjöberget), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589744</v>
+        <v>589753</v>
       </c>
       <c r="R2" t="n">
-        <v>7032178</v>
+        <v>7032196</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118550997</v>
+        <v>118550775</v>
       </c>
       <c r="B3" t="n">
-        <v>57443</v>
+        <v>78484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mellgårdssjöberget (Mellgårdssjöberget), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589736</v>
+        <v>589753</v>
       </c>
       <c r="R3" t="n">
-        <v>7032212</v>
+        <v>7032196</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118550786</v>
+        <v>118550797</v>
       </c>
       <c r="B4" t="n">
-        <v>90788</v>
+        <v>90469</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118550760</v>
+        <v>118550742</v>
       </c>
       <c r="B5" t="n">
-        <v>90504</v>
+        <v>90469</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,38 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mellgårdssjöberget (Mellgårdssjöberget), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589753</v>
+        <v>589744</v>
       </c>
       <c r="R5" t="n">
-        <v>7032196</v>
+        <v>7032178</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118550797</v>
+        <v>118550786</v>
       </c>
       <c r="B6" t="n">
-        <v>90469</v>
+        <v>90788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118550775</v>
+        <v>118550997</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>57443</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,34 +1201,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mellgårdssjöberget (Mellgårdssjöberget), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589753</v>
+        <v>589736</v>
       </c>
       <c r="R7" t="n">
-        <v>7032196</v>
+        <v>7032212</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 29101-2024 artfynd.xlsx
+++ b/artfynd/A 29101-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118550760</v>
+        <v>118550786</v>
       </c>
       <c r="B2" t="n">
-        <v>90504</v>
+        <v>90788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589753</v>
+        <v>589752</v>
       </c>
       <c r="R2" t="n">
-        <v>7032196</v>
+        <v>7032199</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118550775</v>
+        <v>118550742</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>90469</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mellgårdssjöberget (Mellgårdssjöberget), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589753</v>
+        <v>589744</v>
       </c>
       <c r="R3" t="n">
-        <v>7032196</v>
+        <v>7032178</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118550797</v>
+        <v>118550997</v>
       </c>
       <c r="B4" t="n">
-        <v>90469</v>
+        <v>57443</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mellgårdssjöberget (Mellgårdssjöberget), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589752</v>
+        <v>589736</v>
       </c>
       <c r="R4" t="n">
-        <v>7032199</v>
+        <v>7032212</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118550742</v>
+        <v>118550775</v>
       </c>
       <c r="B5" t="n">
-        <v>90469</v>
+        <v>78484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Mellgårdssjöberget (Mellgårdssjöberget), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589744</v>
+        <v>589753</v>
       </c>
       <c r="R5" t="n">
-        <v>7032178</v>
+        <v>7032196</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118550786</v>
+        <v>118550797</v>
       </c>
       <c r="B6" t="n">
-        <v>90788</v>
+        <v>90469</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118550997</v>
+        <v>118550760</v>
       </c>
       <c r="B7" t="n">
-        <v>57443</v>
+        <v>90504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,39 +1206,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mellgårdssjöberget (Mellgårdssjöberget), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589736</v>
+        <v>589753</v>
       </c>
       <c r="R7" t="n">
-        <v>7032212</v>
+        <v>7032196</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 29101-2024 artfynd.xlsx
+++ b/artfynd/A 29101-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118550786</v>
       </c>
       <c r="B2" t="n">
-        <v>90788</v>
+        <v>90795</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118550742</v>
+        <v>118550797</v>
       </c>
       <c r="B3" t="n">
-        <v>90469</v>
+        <v>90476</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Mellgårdssjöberget (Mellgårdssjöberget), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589744</v>
+        <v>589752</v>
       </c>
       <c r="R3" t="n">
-        <v>7032178</v>
+        <v>7032199</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118550997</v>
+        <v>118550742</v>
       </c>
       <c r="B4" t="n">
-        <v>57443</v>
+        <v>90476</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,43 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mellgårdssjöberget (Mellgårdssjöberget), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589736</v>
+        <v>589744</v>
       </c>
       <c r="R4" t="n">
-        <v>7032212</v>
+        <v>7032178</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -989,7 +984,7 @@
         <v>118550775</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118550797</v>
+        <v>118550760</v>
       </c>
       <c r="B6" t="n">
-        <v>90469</v>
+        <v>90511</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589752</v>
+        <v>589753</v>
       </c>
       <c r="R6" t="n">
-        <v>7032199</v>
+        <v>7032196</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118550760</v>
+        <v>118550997</v>
       </c>
       <c r="B7" t="n">
-        <v>90504</v>
+        <v>57443</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,34 +1201,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mellgårdssjöberget (Mellgårdssjöberget), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589753</v>
+        <v>589736</v>
       </c>
       <c r="R7" t="n">
-        <v>7032196</v>
+        <v>7032212</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 29101-2024 artfynd.xlsx
+++ b/artfynd/A 29101-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118550786</v>
+        <v>118550797</v>
       </c>
       <c r="B2" t="n">
-        <v>90795</v>
+        <v>90476</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118550797</v>
+        <v>118550786</v>
       </c>
       <c r="B3" t="n">
-        <v>90476</v>
+        <v>90795</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118550742</v>
+        <v>118550760</v>
       </c>
       <c r="B4" t="n">
-        <v>90476</v>
+        <v>90511</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
+          <t>Mellgårdssjöberget (Mellgårdssjöberget), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589744</v>
+        <v>589753</v>
       </c>
       <c r="R4" t="n">
-        <v>7032178</v>
+        <v>7032196</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118550775</v>
+        <v>118550742</v>
       </c>
       <c r="B5" t="n">
-        <v>78491</v>
+        <v>90476</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mellgårdssjöberget (Mellgårdssjöberget), Ång</t>
+          <t>Norr-Hållmyrflon (Norr-Hållmyrflon), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589753</v>
+        <v>589744</v>
       </c>
       <c r="R5" t="n">
-        <v>7032196</v>
+        <v>7032178</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118550760</v>
+        <v>118550997</v>
       </c>
       <c r="B6" t="n">
-        <v>90511</v>
+        <v>57443</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1099,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mellgårdssjöberget (Mellgårdssjöberget), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589753</v>
+        <v>589736</v>
       </c>
       <c r="R6" t="n">
-        <v>7032196</v>
+        <v>7032212</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118550997</v>
+        <v>118550775</v>
       </c>
       <c r="B7" t="n">
-        <v>57443</v>
+        <v>78491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,39 +1206,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mellgårdssjöberget (Mellgårdssjöberget), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589736</v>
+        <v>589753</v>
       </c>
       <c r="R7" t="n">
-        <v>7032212</v>
+        <v>7032196</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 29101-2024 artfynd.xlsx
+++ b/artfynd/A 29101-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1290,6 +1290,622 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122217393</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78639</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>589663</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7032279</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122217858</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98149</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>589680</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7032243</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122217555</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91194</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>589698</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7032235</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122216954</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78639</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>589577</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7032370</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122217584</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90719</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>589694</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7032237</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122217669</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78639</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>589734</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7032234</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29101-2024 artfynd.xlsx
+++ b/artfynd/A 29101-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1906,6 +1906,117 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122218094</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98157</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Norr-hållmyrflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>589596</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7032349</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29101-2024 artfynd.xlsx
+++ b/artfynd/A 29101-2024 artfynd.xlsx
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122217393</v>
+        <v>122217858</v>
       </c>
       <c r="B8" t="n">
-        <v>78639</v>
+        <v>98157</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,38 +1304,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589663</v>
+        <v>589680</v>
       </c>
       <c r="R8" t="n">
-        <v>7032279</v>
+        <v>7032243</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122217858</v>
+        <v>122217584</v>
       </c>
       <c r="B9" t="n">
-        <v>98149</v>
+        <v>90726</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,42 +1410,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589680</v>
+        <v>589694</v>
       </c>
       <c r="R9" t="n">
-        <v>7032243</v>
+        <v>7032237</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1503,7 +1503,7 @@
         <v>122217555</v>
       </c>
       <c r="B10" t="n">
-        <v>91194</v>
+        <v>91201</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122216954</v>
+        <v>122217669</v>
       </c>
       <c r="B11" t="n">
-        <v>78639</v>
+        <v>78643</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,14 +1638,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
+          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589577</v>
+        <v>589734</v>
       </c>
       <c r="R11" t="n">
-        <v>7032370</v>
+        <v>7032234</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122217584</v>
+        <v>122217393</v>
       </c>
       <c r="B12" t="n">
-        <v>90719</v>
+        <v>78643</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,25 +1716,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589694</v>
+        <v>589663</v>
       </c>
       <c r="R12" t="n">
-        <v>7032237</v>
+        <v>7032279</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122217669</v>
+        <v>122216954</v>
       </c>
       <c r="B13" t="n">
-        <v>78639</v>
+        <v>78643</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1842,14 +1842,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589734</v>
+        <v>589577</v>
       </c>
       <c r="R13" t="n">
-        <v>7032234</v>
+        <v>7032370</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 29101-2024 artfynd.xlsx
+++ b/artfynd/A 29101-2024 artfynd.xlsx
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122217858</v>
+        <v>122217555</v>
       </c>
       <c r="B8" t="n">
-        <v>98157</v>
+        <v>91203</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,38 +1308,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589680</v>
+        <v>589698</v>
       </c>
       <c r="R8" t="n">
-        <v>7032243</v>
+        <v>7032235</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1401,7 +1397,7 @@
         <v>122217584</v>
       </c>
       <c r="B9" t="n">
-        <v>90726</v>
+        <v>90728</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122217555</v>
+        <v>122216954</v>
       </c>
       <c r="B10" t="n">
-        <v>91201</v>
+        <v>78645</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589698</v>
+        <v>589577</v>
       </c>
       <c r="R10" t="n">
-        <v>7032235</v>
+        <v>7032370</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1602,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122217669</v>
+        <v>122217393</v>
       </c>
       <c r="B11" t="n">
-        <v>78643</v>
+        <v>78645</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,14 +1634,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589734</v>
+        <v>589663</v>
       </c>
       <c r="R11" t="n">
-        <v>7032234</v>
+        <v>7032279</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1704,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122217393</v>
+        <v>122217858</v>
       </c>
       <c r="B12" t="n">
-        <v>78643</v>
+        <v>98159</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,38 +1712,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589663</v>
+        <v>589680</v>
       </c>
       <c r="R12" t="n">
-        <v>7032279</v>
+        <v>7032243</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122216954</v>
+        <v>122217669</v>
       </c>
       <c r="B13" t="n">
-        <v>78643</v>
+        <v>78645</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1842,14 +1842,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
+          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589577</v>
+        <v>589734</v>
       </c>
       <c r="R13" t="n">
-        <v>7032370</v>
+        <v>7032234</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1911,7 +1911,7 @@
         <v>122218094</v>
       </c>
       <c r="B14" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 29101-2024 artfynd.xlsx
+++ b/artfynd/A 29101-2024 artfynd.xlsx
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122217584</v>
+        <v>122217858</v>
       </c>
       <c r="B9" t="n">
-        <v>90728</v>
+        <v>98159</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,38 +1406,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589694</v>
+        <v>589680</v>
       </c>
       <c r="R9" t="n">
-        <v>7032237</v>
+        <v>7032243</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,7 +1500,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122216954</v>
+        <v>122217393</v>
       </c>
       <c r="B10" t="n">
         <v>78645</v>
@@ -1536,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589577</v>
+        <v>589663</v>
       </c>
       <c r="R10" t="n">
-        <v>7032370</v>
+        <v>7032279</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,7 +1602,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122217393</v>
+        <v>122217669</v>
       </c>
       <c r="B11" t="n">
         <v>78645</v>
@@ -1634,14 +1638,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
+          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589663</v>
+        <v>589734</v>
       </c>
       <c r="R11" t="n">
-        <v>7032279</v>
+        <v>7032234</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122217858</v>
+        <v>122216954</v>
       </c>
       <c r="B12" t="n">
-        <v>98159</v>
+        <v>78645</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,42 +1716,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589680</v>
+        <v>589577</v>
       </c>
       <c r="R12" t="n">
-        <v>7032243</v>
+        <v>7032370</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122217669</v>
+        <v>122217584</v>
       </c>
       <c r="B13" t="n">
-        <v>78645</v>
+        <v>90728</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,38 +1818,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589734</v>
+        <v>589694</v>
       </c>
       <c r="R13" t="n">
-        <v>7032234</v>
+        <v>7032237</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 29101-2024 artfynd.xlsx
+++ b/artfynd/A 29101-2024 artfynd.xlsx
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122217858</v>
+        <v>122217393</v>
       </c>
       <c r="B8" t="n">
-        <v>98175</v>
+        <v>78645</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,42 +1304,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589680</v>
+        <v>589663</v>
       </c>
       <c r="R8" t="n">
-        <v>7032243</v>
+        <v>7032279</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1398,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122216954</v>
+        <v>122217584</v>
       </c>
       <c r="B9" t="n">
-        <v>78645</v>
+        <v>90744</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589577</v>
+        <v>589694</v>
       </c>
       <c r="R9" t="n">
-        <v>7032370</v>
+        <v>7032237</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122217555</v>
+        <v>122217669</v>
       </c>
       <c r="B10" t="n">
-        <v>91219</v>
+        <v>78645</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,38 +1508,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
+          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589698</v>
+        <v>589734</v>
       </c>
       <c r="R10" t="n">
-        <v>7032235</v>
+        <v>7032234</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1602,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122217393</v>
+        <v>122217555</v>
       </c>
       <c r="B11" t="n">
-        <v>78645</v>
+        <v>91219</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589663</v>
+        <v>589698</v>
       </c>
       <c r="R11" t="n">
-        <v>7032279</v>
+        <v>7032235</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1704,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122217584</v>
+        <v>122216954</v>
       </c>
       <c r="B12" t="n">
-        <v>90744</v>
+        <v>78645</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589694</v>
+        <v>589577</v>
       </c>
       <c r="R12" t="n">
-        <v>7032237</v>
+        <v>7032370</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1806,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122217669</v>
+        <v>122217858</v>
       </c>
       <c r="B13" t="n">
-        <v>78645</v>
+        <v>98175</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,38 +1814,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589734</v>
+        <v>589680</v>
       </c>
       <c r="R13" t="n">
-        <v>7032234</v>
+        <v>7032243</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 29101-2024 artfynd.xlsx
+++ b/artfynd/A 29101-2024 artfynd.xlsx
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122217393</v>
+        <v>122216954</v>
       </c>
       <c r="B8" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589663</v>
+        <v>589577</v>
       </c>
       <c r="R8" t="n">
-        <v>7032279</v>
+        <v>7032370</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1397,7 +1397,7 @@
         <v>122217584</v>
       </c>
       <c r="B9" t="n">
-        <v>90744</v>
+        <v>90754</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122217669</v>
+        <v>122217393</v>
       </c>
       <c r="B10" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,14 +1532,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589734</v>
+        <v>589663</v>
       </c>
       <c r="R10" t="n">
-        <v>7032234</v>
+        <v>7032279</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1601,7 +1601,7 @@
         <v>122217555</v>
       </c>
       <c r="B11" t="n">
-        <v>91219</v>
+        <v>91229</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122216954</v>
+        <v>122217669</v>
       </c>
       <c r="B12" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,14 +1736,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
+          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589577</v>
+        <v>589734</v>
       </c>
       <c r="R12" t="n">
-        <v>7032370</v>
+        <v>7032234</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1805,7 +1805,7 @@
         <v>122217858</v>
       </c>
       <c r="B13" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>122218094</v>
       </c>
       <c r="B14" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 29101-2024 artfynd.xlsx
+++ b/artfynd/A 29101-2024 artfynd.xlsx
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122217584</v>
+        <v>122217555</v>
       </c>
       <c r="B9" t="n">
-        <v>90754</v>
+        <v>91229</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589694</v>
+        <v>589698</v>
       </c>
       <c r="R9" t="n">
-        <v>7032237</v>
+        <v>7032235</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122217393</v>
+        <v>122217669</v>
       </c>
       <c r="B10" t="n">
         <v>78646</v>
@@ -1532,14 +1532,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
+          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589663</v>
+        <v>589734</v>
       </c>
       <c r="R10" t="n">
-        <v>7032279</v>
+        <v>7032234</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122217555</v>
+        <v>122217393</v>
       </c>
       <c r="B11" t="n">
-        <v>91229</v>
+        <v>78646</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589698</v>
+        <v>589663</v>
       </c>
       <c r="R11" t="n">
-        <v>7032235</v>
+        <v>7032279</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122217669</v>
+        <v>122217858</v>
       </c>
       <c r="B12" t="n">
-        <v>78646</v>
+        <v>98185</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,38 +1712,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589734</v>
+        <v>589680</v>
       </c>
       <c r="R12" t="n">
-        <v>7032234</v>
+        <v>7032243</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1802,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122217858</v>
+        <v>122217584</v>
       </c>
       <c r="B13" t="n">
-        <v>98185</v>
+        <v>90754</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,42 +1818,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589680</v>
+        <v>589694</v>
       </c>
       <c r="R13" t="n">
-        <v>7032243</v>
+        <v>7032237</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 29101-2024 artfynd.xlsx
+++ b/artfynd/A 29101-2024 artfynd.xlsx
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122216954</v>
+        <v>122217669</v>
       </c>
       <c r="B8" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,14 +1328,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
+          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589577</v>
+        <v>589734</v>
       </c>
       <c r="R8" t="n">
-        <v>7032370</v>
+        <v>7032234</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122217555</v>
+        <v>122217858</v>
       </c>
       <c r="B9" t="n">
-        <v>91229</v>
+        <v>98197</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,34 +1410,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589698</v>
+        <v>589680</v>
       </c>
       <c r="R9" t="n">
-        <v>7032235</v>
+        <v>7032243</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122217669</v>
+        <v>122216954</v>
       </c>
       <c r="B10" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,14 +1536,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589734</v>
+        <v>589577</v>
       </c>
       <c r="R10" t="n">
-        <v>7032234</v>
+        <v>7032370</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122217393</v>
+        <v>122217555</v>
       </c>
       <c r="B11" t="n">
-        <v>78646</v>
+        <v>91241</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589663</v>
+        <v>589698</v>
       </c>
       <c r="R11" t="n">
-        <v>7032279</v>
+        <v>7032235</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122217858</v>
+        <v>122217393</v>
       </c>
       <c r="B12" t="n">
-        <v>98185</v>
+        <v>78651</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,42 +1716,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589680</v>
+        <v>589663</v>
       </c>
       <c r="R12" t="n">
-        <v>7032243</v>
+        <v>7032279</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1809,7 +1809,7 @@
         <v>122217584</v>
       </c>
       <c r="B13" t="n">
-        <v>90754</v>
+        <v>90766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>122218094</v>
       </c>
       <c r="B14" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 29101-2024 artfynd.xlsx
+++ b/artfynd/A 29101-2024 artfynd.xlsx
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122217669</v>
+        <v>122217858</v>
       </c>
       <c r="B8" t="n">
-        <v>78651</v>
+        <v>98202</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,38 +1304,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589734</v>
+        <v>589680</v>
       </c>
       <c r="R8" t="n">
-        <v>7032234</v>
+        <v>7032243</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122217858</v>
+        <v>122217393</v>
       </c>
       <c r="B9" t="n">
-        <v>98197</v>
+        <v>78651</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,42 +1410,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589680</v>
+        <v>589663</v>
       </c>
       <c r="R9" t="n">
-        <v>7032243</v>
+        <v>7032279</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122216954</v>
+        <v>122217555</v>
       </c>
       <c r="B10" t="n">
-        <v>78651</v>
+        <v>91246</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589577</v>
+        <v>589698</v>
       </c>
       <c r="R10" t="n">
-        <v>7032370</v>
+        <v>7032235</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122217555</v>
+        <v>122216954</v>
       </c>
       <c r="B11" t="n">
-        <v>91241</v>
+        <v>78651</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589698</v>
+        <v>589577</v>
       </c>
       <c r="R11" t="n">
-        <v>7032235</v>
+        <v>7032370</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122217393</v>
+        <v>122217669</v>
       </c>
       <c r="B12" t="n">
         <v>78651</v>
@@ -1740,14 +1740,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
+          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589663</v>
+        <v>589734</v>
       </c>
       <c r="R12" t="n">
-        <v>7032279</v>
+        <v>7032234</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1809,7 +1809,7 @@
         <v>122217584</v>
       </c>
       <c r="B13" t="n">
-        <v>90766</v>
+        <v>90773</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>122218094</v>
       </c>
       <c r="B14" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 29101-2024 artfynd.xlsx
+++ b/artfynd/A 29101-2024 artfynd.xlsx
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122217858</v>
+        <v>122217393</v>
       </c>
       <c r="B8" t="n">
-        <v>98202</v>
+        <v>78652</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,42 +1304,33 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589680</v>
+        <v>589663</v>
       </c>
       <c r="R8" t="n">
-        <v>7032243</v>
+        <v>7032279</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1398,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122217393</v>
+        <v>122217669</v>
       </c>
       <c r="B9" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,11 +1407,6 @@
       <c r="E9" t="n">
         <v>6425</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1434,14 +1420,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
+          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589663</v>
+        <v>589734</v>
       </c>
       <c r="R9" t="n">
-        <v>7032279</v>
+        <v>7032234</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1503,7 +1489,7 @@
         <v>122217555</v>
       </c>
       <c r="B10" t="n">
-        <v>91246</v>
+        <v>91251</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,11 +1503,6 @@
       </c>
       <c r="E10" t="n">
         <v>1209</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1605,7 +1586,7 @@
         <v>122216954</v>
       </c>
       <c r="B11" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,11 +1600,6 @@
       </c>
       <c r="E11" t="n">
         <v>6425</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1704,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122217669</v>
+        <v>122217858</v>
       </c>
       <c r="B12" t="n">
-        <v>78651</v>
+        <v>98211</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,38 +1692,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589734</v>
+        <v>589680</v>
       </c>
       <c r="R12" t="n">
-        <v>7032234</v>
+        <v>7032243</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1809,7 +1784,7 @@
         <v>122217584</v>
       </c>
       <c r="B13" t="n">
-        <v>90773</v>
+        <v>90778</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,11 +1798,6 @@
       </c>
       <c r="E13" t="n">
         <v>5447</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1911,7 +1881,7 @@
         <v>122218094</v>
       </c>
       <c r="B14" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,11 +1895,6 @@
       </c>
       <c r="E14" t="n">
         <v>220787</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>

--- a/artfynd/A 29101-2024 artfynd.xlsx
+++ b/artfynd/A 29101-2024 artfynd.xlsx
@@ -1295,7 +1295,7 @@
         <v>122217393</v>
       </c>
       <c r="B8" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,6 +1309,11 @@
       </c>
       <c r="E8" t="n">
         <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1389,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122217669</v>
+        <v>122217858</v>
       </c>
       <c r="B9" t="n">
-        <v>78652</v>
+        <v>98224</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,33 +1406,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589734</v>
+        <v>589680</v>
       </c>
       <c r="R9" t="n">
-        <v>7032234</v>
+        <v>7032243</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1486,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122217555</v>
+        <v>122217584</v>
       </c>
       <c r="B10" t="n">
-        <v>91251</v>
+        <v>90791</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1498,20 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>5447</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1521,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589698</v>
+        <v>589694</v>
       </c>
       <c r="R10" t="n">
-        <v>7032235</v>
+        <v>7032237</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1583,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122216954</v>
+        <v>122217555</v>
       </c>
       <c r="B11" t="n">
-        <v>78652</v>
+        <v>91264</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1595,20 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1209</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589577</v>
+        <v>589698</v>
       </c>
       <c r="R11" t="n">
-        <v>7032370</v>
+        <v>7032235</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1680,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122217858</v>
+        <v>122216954</v>
       </c>
       <c r="B12" t="n">
-        <v>98211</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1692,37 +1716,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589680</v>
+        <v>589577</v>
       </c>
       <c r="R12" t="n">
-        <v>7032243</v>
+        <v>7032370</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1781,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122217584</v>
+        <v>122217669</v>
       </c>
       <c r="B13" t="n">
-        <v>90778</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1793,33 +1818,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
+          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589694</v>
+        <v>589734</v>
       </c>
       <c r="R13" t="n">
-        <v>7032237</v>
+        <v>7032234</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1881,7 +1911,7 @@
         <v>122218094</v>
       </c>
       <c r="B14" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1895,6 +1925,11 @@
       </c>
       <c r="E14" t="n">
         <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>

--- a/artfynd/A 29101-2024 artfynd.xlsx
+++ b/artfynd/A 29101-2024 artfynd.xlsx
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122217393</v>
+        <v>122217669</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1328,14 +1328,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
+          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589663</v>
+        <v>589734</v>
       </c>
       <c r="R8" t="n">
-        <v>7032279</v>
+        <v>7032234</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122217858</v>
+        <v>122217584</v>
       </c>
       <c r="B9" t="n">
-        <v>98224</v>
+        <v>90804</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,42 +1406,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589680</v>
+        <v>589694</v>
       </c>
       <c r="R9" t="n">
-        <v>7032243</v>
+        <v>7032237</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122217584</v>
+        <v>122217858</v>
       </c>
       <c r="B10" t="n">
-        <v>90791</v>
+        <v>98237</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,38 +1508,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589694</v>
+        <v>589680</v>
       </c>
       <c r="R10" t="n">
-        <v>7032237</v>
+        <v>7032243</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122217555</v>
+        <v>122216954</v>
       </c>
       <c r="B11" t="n">
-        <v>91264</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589698</v>
+        <v>589577</v>
       </c>
       <c r="R11" t="n">
-        <v>7032235</v>
+        <v>7032370</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122216954</v>
+        <v>122217393</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589577</v>
+        <v>589663</v>
       </c>
       <c r="R12" t="n">
-        <v>7032370</v>
+        <v>7032279</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122217669</v>
+        <v>122217555</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>91277</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,38 +1818,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589734</v>
+        <v>589698</v>
       </c>
       <c r="R13" t="n">
-        <v>7032234</v>
+        <v>7032235</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1911,7 +1911,7 @@
         <v>122218094</v>
       </c>
       <c r="B14" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 29101-2024 artfynd.xlsx
+++ b/artfynd/A 29101-2024 artfynd.xlsx
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122217669</v>
+        <v>122216954</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1328,14 +1328,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589734</v>
+        <v>589577</v>
       </c>
       <c r="R8" t="n">
-        <v>7032234</v>
+        <v>7032370</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122217584</v>
+        <v>122217393</v>
       </c>
       <c r="B9" t="n">
-        <v>90804</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589694</v>
+        <v>589663</v>
       </c>
       <c r="R9" t="n">
-        <v>7032237</v>
+        <v>7032279</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122216954</v>
+        <v>122217669</v>
       </c>
       <c r="B11" t="n">
         <v>78656</v>
@@ -1638,14 +1638,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
+          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589577</v>
+        <v>589734</v>
       </c>
       <c r="R11" t="n">
-        <v>7032370</v>
+        <v>7032234</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122217393</v>
+        <v>122217555</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>91277</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,25 +1716,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589663</v>
+        <v>589698</v>
       </c>
       <c r="R12" t="n">
-        <v>7032279</v>
+        <v>7032235</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122217555</v>
+        <v>122217584</v>
       </c>
       <c r="B13" t="n">
-        <v>91277</v>
+        <v>90804</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,25 +1818,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589698</v>
+        <v>589694</v>
       </c>
       <c r="R13" t="n">
-        <v>7032235</v>
+        <v>7032237</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 29101-2024 artfynd.xlsx
+++ b/artfynd/A 29101-2024 artfynd.xlsx
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122216954</v>
+        <v>122217669</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1328,14 +1328,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
+          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589577</v>
+        <v>589734</v>
       </c>
       <c r="R8" t="n">
-        <v>7032370</v>
+        <v>7032234</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122217858</v>
+        <v>122216954</v>
       </c>
       <c r="B10" t="n">
-        <v>98237</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,42 +1508,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589680</v>
+        <v>589577</v>
       </c>
       <c r="R10" t="n">
-        <v>7032243</v>
+        <v>7032370</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1602,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122217669</v>
+        <v>122217555</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>91278</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,38 +1610,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mellgårdssjöberget, Mellgårdssjöberget, Ång</t>
+          <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589734</v>
+        <v>589698</v>
       </c>
       <c r="R11" t="n">
-        <v>7032234</v>
+        <v>7032235</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1704,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122217555</v>
+        <v>122217584</v>
       </c>
       <c r="B12" t="n">
-        <v>91277</v>
+        <v>90798</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589698</v>
+        <v>589694</v>
       </c>
       <c r="R12" t="n">
-        <v>7032235</v>
+        <v>7032237</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1806,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122217584</v>
+        <v>122217858</v>
       </c>
       <c r="B13" t="n">
-        <v>90804</v>
+        <v>98240</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,38 +1814,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Norr-Hållmyrflon, Norr-Hållmyrflon, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589694</v>
+        <v>589680</v>
       </c>
       <c r="R13" t="n">
-        <v>7032237</v>
+        <v>7032243</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1911,7 +1911,7 @@
         <v>122218094</v>
       </c>
       <c r="B14" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 29101-2024 artfynd.xlsx
+++ b/artfynd/A 29101-2024 artfynd.xlsx
@@ -1911,7 +1911,7 @@
         <v>122218094</v>
       </c>
       <c r="B14" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
